--- a/pz1/Земляник - ПЗ1 Таблицы TableMind.xlsx
+++ b/pz1/Земляник - ПЗ1 Таблицы TableMind.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\excel-mcp-files\project-management-tablemind\pz1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1892544C-1684-40BC-92D9-FE3876A11640}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BB36EF9-7EDD-44E9-B214-78C39528E5A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2670" yWindow="458" windowWidth="12023" windowHeight="10972" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3008" yWindow="458" windowWidth="12022" windowHeight="10972" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Титул" sheetId="1" r:id="rId1"/>
@@ -179,7 +179,7 @@
     <t>Стоимость 1 чел.-мес., BYN</t>
   </si>
   <si>
-    <t>5 600 BYN брутто + 34% взносов ФСЗН</t>
+    <t>5 600 брутто + 34% ФСЗН = 7 504, округлено</t>
   </si>
   <si>
     <t>Резерв на риски, % от базовой стоимости</t>
@@ -820,8 +820,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="165" formatCode="#\ ##0"/>
-    <numFmt numFmtId="166" formatCode="dd\.mm\.yyyy"/>
+    <numFmt numFmtId="164" formatCode="#\ ##0"/>
+    <numFmt numFmtId="165" formatCode="dd\.mm\.yyyy"/>
   </numFmts>
   <fonts count="10" x14ac:knownFonts="1">
     <font>
@@ -975,9 +975,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -1011,20 +1008,8 @@
     <xf numFmtId="1" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1053,16 +1038,31 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -1291,7 +1291,7 @@
           <c:smooth val="1"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-749E-4714-B09A-5D07CD325DE0}"/>
+              <c16:uniqueId val="{00000000-D1BC-4FED-A8D8-0F09941A0142}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1717,33 +1717,33 @@
   <dimension ref="A1:B24"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="30" customWidth="1"/>
-    <col min="2" max="2" width="95" customWidth="1"/>
+    <col min="1" max="1" width="30" style="29" customWidth="1"/>
+    <col min="2" max="2" width="95" style="29" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="36" customFormat="1" ht="18" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="35"/>
-    </row>
-    <row r="2" spans="1:2" s="36" customFormat="1" ht="18" x14ac:dyDescent="0.45">
+      <c r="B1" s="28"/>
+    </row>
+    <row r="2" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="35"/>
-    </row>
-    <row r="3" spans="1:2" ht="18" x14ac:dyDescent="0.45">
+      <c r="B2" s="28"/>
+    </row>
+    <row r="3" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="2"/>
     </row>
-    <row r="4" spans="1:2" ht="15.75" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
     </row>
-    <row r="5" spans="1:2" ht="15.75" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="5" t="s">
         <v>3</v>
       </c>
@@ -1751,7 +1751,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="15.75" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A6" s="5" t="s">
         <v>5</v>
       </c>
@@ -1759,7 +1759,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="15.75" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A7" s="5" t="s">
         <v>7</v>
       </c>
@@ -1767,17 +1767,17 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="15.75" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
     </row>
-    <row r="9" spans="1:2" ht="15.75" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A9" s="4" t="s">
         <v>9</v>
       </c>
       <c r="B9" s="2"/>
     </row>
-    <row r="10" spans="1:2" ht="15.75" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A10" s="6" t="s">
         <v>10</v>
       </c>
@@ -1785,7 +1785,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="15.75" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A11" s="6" t="s">
         <v>12</v>
       </c>
@@ -1794,25 +1794,25 @@
         <v>57 чел.-мес., 7 человек</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="15.75" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A12" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="7">
+      <c r="B12" s="30">
         <f>'Команда и бюджет'!C24</f>
         <v>517000</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="15.75" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A13" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="B13" s="7">
+      <c r="B13" s="30">
         <f>'Команда и бюджет'!C23</f>
         <v>47000</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="15.75" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A14" s="6" t="s">
         <v>15</v>
       </c>
@@ -1821,7 +1821,7 @@
         <v>8 из 18 (44%)</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="15.75" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A15" s="6" t="s">
         <v>16</v>
       </c>
@@ -1829,17 +1829,17 @@
         <v>17</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="15.75" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
     </row>
-    <row r="17" spans="1:2" ht="15.75" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A17" s="4" t="s">
         <v>18</v>
       </c>
       <c r="B17" s="2"/>
     </row>
-    <row r="18" spans="1:2" ht="31.5" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:2" ht="31.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A18" s="5" t="s">
         <v>19</v>
       </c>
@@ -1847,7 +1847,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="15.75" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A19" s="5" t="s">
         <v>21</v>
       </c>
@@ -1855,7 +1855,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="15.75" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A20" s="5" t="s">
         <v>23</v>
       </c>
@@ -1863,7 +1863,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="15.75" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A21" s="5" t="s">
         <v>25</v>
       </c>
@@ -1871,7 +1871,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="22" spans="1:2" ht="15.75" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A22" s="5" t="s">
         <v>27</v>
       </c>
@@ -1879,19 +1879,19 @@
         <v>28</v>
       </c>
     </row>
-    <row r="23" spans="1:2" ht="15.75" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
     </row>
-    <row r="24" spans="1:2" ht="15.75" x14ac:dyDescent="0.45">
-      <c r="A24" s="8" t="s">
+    <row r="24" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A24" s="7" t="s">
         <v>29</v>
       </c>
       <c r="B24" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" fitToHeight="0" orientation="landscape"/>
   <headerFooter>
     <oddFooter>&amp;C&amp;P / &amp;N</oddFooter>
   </headerFooter>
@@ -1907,221 +1907,221 @@
   <dimension ref="A1:E25"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
-    <col min="2" max="2" width="52" customWidth="1"/>
-    <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="36" customWidth="1"/>
-    <col min="5" max="5" width="12" customWidth="1"/>
+    <col min="1" max="1" width="6" style="29" customWidth="1"/>
+    <col min="2" max="2" width="52" style="29" customWidth="1"/>
+    <col min="3" max="3" width="14" style="29" customWidth="1"/>
+    <col min="4" max="4" width="36" style="29" customWidth="1"/>
+    <col min="5" max="5" width="12" style="29" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="36" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="36" t="s">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:5" s="36" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="11" t="s">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A2" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="B2" s="9"/>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
+      <c r="B2" s="8"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="8"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A3" s="9"/>
-      <c r="B3" s="9"/>
-      <c r="C3" s="9"/>
-      <c r="D3" s="9"/>
-      <c r="E3" s="9"/>
+      <c r="A3" s="8"/>
+      <c r="B3" s="8"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="8"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A4" s="10" t="s">
+      <c r="A4" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C4" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="D4" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="E4" s="10" t="s">
+      <c r="E4" s="9" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A5" s="13">
+      <c r="A5" s="12">
         <v>1</v>
       </c>
-      <c r="B5" s="12" t="s">
+      <c r="B5" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="C5" s="15">
+      <c r="C5" s="14">
         <v>0.5</v>
       </c>
-      <c r="D5" s="14">
+      <c r="D5" s="13">
         <v>12</v>
       </c>
-      <c r="E5" s="16">
+      <c r="E5" s="15">
         <f t="shared" ref="E5:E11" si="0">C5*D5</f>
         <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A6" s="13">
+      <c r="A6" s="12">
         <v>2</v>
       </c>
-      <c r="B6" s="12" t="s">
+      <c r="B6" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="C6" s="15">
+      <c r="C6" s="14">
         <v>1</v>
       </c>
-      <c r="D6" s="14">
+      <c r="D6" s="13">
         <v>12</v>
       </c>
-      <c r="E6" s="16">
+      <c r="E6" s="15">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A7" s="13">
+      <c r="A7" s="12">
         <v>3</v>
       </c>
-      <c r="B7" s="12" t="s">
+      <c r="B7" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="C7" s="15">
+      <c r="C7" s="14">
         <v>1</v>
       </c>
-      <c r="D7" s="14">
+      <c r="D7" s="13">
         <v>11</v>
       </c>
-      <c r="E7" s="16">
+      <c r="E7" s="15">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A8" s="13">
+      <c r="A8" s="12">
         <v>4</v>
       </c>
-      <c r="B8" s="12" t="s">
+      <c r="B8" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="C8" s="15">
+      <c r="C8" s="14">
         <v>1</v>
       </c>
-      <c r="D8" s="14">
+      <c r="D8" s="13">
         <v>10</v>
       </c>
-      <c r="E8" s="16">
+      <c r="E8" s="15">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A9" s="13">
+      <c r="A9" s="12">
         <v>5</v>
       </c>
-      <c r="B9" s="12" t="s">
+      <c r="B9" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="C9" s="15">
+      <c r="C9" s="14">
         <v>1</v>
       </c>
-      <c r="D9" s="14">
+      <c r="D9" s="13">
         <v>10</v>
       </c>
-      <c r="E9" s="16">
+      <c r="E9" s="15">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A10" s="13">
+      <c r="A10" s="12">
         <v>6</v>
       </c>
-      <c r="B10" s="12" t="s">
+      <c r="B10" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="C10" s="15">
+      <c r="C10" s="14">
         <v>0.5</v>
       </c>
-      <c r="D10" s="14">
+      <c r="D10" s="13">
         <v>4</v>
       </c>
-      <c r="E10" s="16">
+      <c r="E10" s="15">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A11" s="13">
+      <c r="A11" s="12">
         <v>7</v>
       </c>
-      <c r="B11" s="12" t="s">
+      <c r="B11" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="C11" s="15">
+      <c r="C11" s="14">
         <v>0.75</v>
       </c>
-      <c r="D11" s="14">
+      <c r="D11" s="13">
         <v>8</v>
       </c>
-      <c r="E11" s="16">
+      <c r="E11" s="15">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A12" s="17"/>
-      <c r="B12" s="17" t="s">
+      <c r="A12" s="16"/>
+      <c r="B12" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="C12" s="17"/>
-      <c r="D12" s="17"/>
-      <c r="E12" s="18">
+      <c r="C12" s="16"/>
+      <c r="D12" s="16"/>
+      <c r="E12" s="17">
         <f>SUM(E5:E11)</f>
         <v>57</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A13" s="9"/>
-      <c r="B13" s="9"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="9"/>
+      <c r="A13" s="8"/>
+      <c r="B13" s="8"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A14" s="9"/>
-      <c r="B14" s="9" t="s">
+      <c r="A14" s="8"/>
+      <c r="B14" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="C14" s="19">
+      <c r="C14" s="31">
         <v>7500</v>
       </c>
-      <c r="D14" s="11" t="s">
+      <c r="D14" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="E14" s="9"/>
+      <c r="E14" s="8"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A15" s="9"/>
-      <c r="B15" s="9" t="s">
+      <c r="A15" s="8"/>
+      <c r="B15" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="C15" s="20">
+      <c r="C15" s="18">
         <v>0.1</v>
       </c>
-      <c r="D15" s="9"/>
-      <c r="E15" s="9"/>
-    </row>
-    <row r="16" spans="1:5" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="D15" s="8"/>
+      <c r="E15" s="8"/>
+    </row>
+    <row r="16" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A16" s="1" t="s">
         <v>32</v>
       </c>
@@ -2134,126 +2134,126 @@
       <c r="D16" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E16" s="9"/>
+      <c r="E16" s="8"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A17" s="13">
+      <c r="A17" s="12">
         <v>1</v>
       </c>
-      <c r="B17" s="12" t="s">
+      <c r="B17" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="C17" s="21">
+      <c r="C17" s="32">
         <f>E12*C14</f>
         <v>427500</v>
       </c>
-      <c r="D17" s="12" t="s">
+      <c r="D17" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="E17" s="9"/>
+      <c r="E17" s="8"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A18" s="13">
+      <c r="A18" s="12">
         <v>2</v>
       </c>
-      <c r="B18" s="12" t="s">
+      <c r="B18" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="C18" s="22">
+      <c r="C18" s="33">
         <v>15000</v>
       </c>
-      <c r="D18" s="12"/>
-      <c r="E18" s="9"/>
+      <c r="D18" s="11"/>
+      <c r="E18" s="8"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A19" s="13">
+      <c r="A19" s="12">
         <v>3</v>
       </c>
-      <c r="B19" s="12" t="s">
+      <c r="B19" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="C19" s="22">
+      <c r="C19" s="33">
         <v>8000</v>
       </c>
-      <c r="D19" s="12"/>
-      <c r="E19" s="9"/>
+      <c r="D19" s="11"/>
+      <c r="E19" s="8"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A20" s="13">
+      <c r="A20" s="12">
         <v>4</v>
       </c>
-      <c r="B20" s="12" t="s">
+      <c r="B20" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="C20" s="22">
+      <c r="C20" s="33">
         <v>5000</v>
       </c>
-      <c r="D20" s="12"/>
-      <c r="E20" s="9"/>
+      <c r="D20" s="11"/>
+      <c r="E20" s="8"/>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A21" s="13">
+      <c r="A21" s="12">
         <v>5</v>
       </c>
-      <c r="B21" s="12" t="s">
+      <c r="B21" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="C21" s="22">
+      <c r="C21" s="33">
         <v>14500</v>
       </c>
-      <c r="D21" s="12"/>
-      <c r="E21" s="9"/>
+      <c r="D21" s="11"/>
+      <c r="E21" s="8"/>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A22" s="17"/>
-      <c r="B22" s="17" t="s">
+      <c r="A22" s="16"/>
+      <c r="B22" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="C22" s="23">
+      <c r="C22" s="34">
         <f>SUM(C17:C21)</f>
         <v>470000</v>
       </c>
-      <c r="D22" s="17"/>
-      <c r="E22" s="9"/>
+      <c r="D22" s="16"/>
+      <c r="E22" s="8"/>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A23" s="17"/>
-      <c r="B23" s="17" t="s">
+      <c r="A23" s="16"/>
+      <c r="B23" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="C23" s="23">
+      <c r="C23" s="34">
         <f>C22*C15</f>
         <v>47000</v>
       </c>
-      <c r="D23" s="17" t="s">
+      <c r="D23" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="E23" s="9"/>
+      <c r="E23" s="8"/>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A24" s="17"/>
-      <c r="B24" s="17" t="s">
+      <c r="A24" s="16"/>
+      <c r="B24" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="C24" s="23">
+      <c r="C24" s="34">
         <f>C22+C23</f>
         <v>517000</v>
       </c>
-      <c r="D24" s="17"/>
-      <c r="E24" s="9"/>
+      <c r="D24" s="16"/>
+      <c r="E24" s="8"/>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A25" s="9"/>
-      <c r="B25" s="11" t="s">
+      <c r="A25" s="8"/>
+      <c r="B25" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="C25" s="9"/>
-      <c r="D25" s="9"/>
-      <c r="E25" s="9"/>
+      <c r="C25" s="8"/>
+      <c r="D25" s="8"/>
+      <c r="E25" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" fitToHeight="0" orientation="landscape"/>
   <headerFooter>
     <oddFooter>&amp;C&amp;P / &amp;N</oddFooter>
   </headerFooter>
@@ -2269,35 +2269,35 @@
   <dimension ref="A1:D32"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9" customWidth="1"/>
-    <col min="2" max="2" width="70" customWidth="1"/>
-    <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="24" customWidth="1"/>
+    <col min="1" max="1" width="9" style="29" customWidth="1"/>
+    <col min="2" max="2" width="70" style="29" customWidth="1"/>
+    <col min="3" max="3" width="14" style="29" customWidth="1"/>
+    <col min="4" max="4" width="24" style="29" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="36" customFormat="1" ht="18" x14ac:dyDescent="0.45">
-      <c r="A1" s="24" t="s">
+    <row r="1" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A1" s="19" t="s">
         <v>62</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-    </row>
-    <row r="2" spans="1:4" s="36" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="11" t="s">
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A2" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="B2" s="9"/>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9"/>
+      <c r="B2" s="8"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A3" s="9"/>
-      <c r="B3" s="9"/>
-      <c r="C3" s="9"/>
-      <c r="D3" s="9"/>
-    </row>
-    <row r="4" spans="1:4" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="A3" s="8"/>
+      <c r="B3" s="8"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="8"/>
+    </row>
+    <row r="4" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
         <v>32</v>
       </c>
@@ -2312,270 +2312,270 @@
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A5" s="13">
+      <c r="A5" s="12">
         <v>1</v>
       </c>
-      <c r="B5" s="12" t="s">
+      <c r="B5" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="C5" s="25" t="s">
+      <c r="C5" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="D5" s="12" t="s">
+      <c r="D5" s="11" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A6" s="13">
+    <row r="6" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A6" s="12">
         <v>2</v>
       </c>
-      <c r="B6" s="12" t="s">
+      <c r="B6" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="C6" s="25" t="s">
+      <c r="C6" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="D6" s="11" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A7" s="13">
+      <c r="A7" s="12">
         <v>3</v>
       </c>
-      <c r="B7" s="12" t="s">
+      <c r="B7" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="C7" s="25" t="s">
+      <c r="C7" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="D7" s="12" t="s">
+      <c r="D7" s="11" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A8" s="13">
+    <row r="8" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A8" s="12">
         <v>4</v>
       </c>
-      <c r="B8" s="12" t="s">
+      <c r="B8" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="C8" s="25" t="s">
+      <c r="C8" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="D8" s="12" t="s">
+      <c r="D8" s="11" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A9" s="13">
+      <c r="A9" s="12">
         <v>5</v>
       </c>
-      <c r="B9" s="12" t="s">
+      <c r="B9" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="C9" s="25" t="s">
+      <c r="C9" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="D9" s="12" t="s">
+      <c r="D9" s="11" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A10" s="13">
+      <c r="A10" s="12">
         <v>6</v>
       </c>
-      <c r="B10" s="12" t="s">
+      <c r="B10" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="C10" s="25" t="s">
+      <c r="C10" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="D10" s="12" t="s">
+      <c r="D10" s="11" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A11" s="13">
+      <c r="A11" s="12">
         <v>7</v>
       </c>
-      <c r="B11" s="12" t="s">
+      <c r="B11" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="C11" s="25" t="s">
+      <c r="C11" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="D11" s="12" t="s">
+      <c r="D11" s="11" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A12" s="13">
+      <c r="A12" s="12">
         <v>8</v>
       </c>
-      <c r="B12" s="12" t="s">
+      <c r="B12" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="C12" s="25" t="s">
+      <c r="C12" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="D12" s="12" t="s">
+      <c r="D12" s="11" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A13" s="13">
+      <c r="A13" s="12">
         <v>9</v>
       </c>
-      <c r="B13" s="12" t="s">
+      <c r="B13" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="C13" s="25" t="s">
+      <c r="C13" s="20" t="s">
         <v>77</v>
       </c>
-      <c r="D13" s="12" t="s">
+      <c r="D13" s="11" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A14" s="13">
+      <c r="A14" s="12">
         <v>10</v>
       </c>
-      <c r="B14" s="12" t="s">
+      <c r="B14" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="C14" s="25" t="s">
+      <c r="C14" s="20" t="s">
         <v>77</v>
       </c>
-      <c r="D14" s="12" t="s">
+      <c r="D14" s="11" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A15" s="13">
+      <c r="A15" s="12">
         <v>11</v>
       </c>
-      <c r="B15" s="12" t="s">
+      <c r="B15" s="11" t="s">
         <v>80</v>
       </c>
-      <c r="C15" s="25" t="s">
+      <c r="C15" s="20" t="s">
         <v>77</v>
       </c>
-      <c r="D15" s="12" t="s">
+      <c r="D15" s="11" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A16" s="13">
+      <c r="A16" s="12">
         <v>12</v>
       </c>
-      <c r="B16" s="12" t="s">
+      <c r="B16" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="C16" s="25" t="s">
+      <c r="C16" s="20" t="s">
         <v>82</v>
       </c>
-      <c r="D16" s="12" t="s">
+      <c r="D16" s="11" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A17" s="13">
+      <c r="A17" s="12">
         <v>13</v>
       </c>
-      <c r="B17" s="12" t="s">
+      <c r="B17" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="C17" s="25" t="s">
+      <c r="C17" s="20" t="s">
         <v>82</v>
       </c>
-      <c r="D17" s="12" t="s">
+      <c r="D17" s="11" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A18" s="13">
+      <c r="A18" s="12">
         <v>14</v>
       </c>
-      <c r="B18" s="12" t="s">
+      <c r="B18" s="11" t="s">
         <v>85</v>
       </c>
-      <c r="C18" s="25" t="s">
+      <c r="C18" s="20" t="s">
         <v>82</v>
       </c>
-      <c r="D18" s="12" t="s">
+      <c r="D18" s="11" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A19" s="13">
+      <c r="A19" s="12">
         <v>15</v>
       </c>
-      <c r="B19" s="12" t="s">
+      <c r="B19" s="11" t="s">
         <v>86</v>
       </c>
-      <c r="C19" s="25" t="s">
+      <c r="C19" s="20" t="s">
         <v>87</v>
       </c>
-      <c r="D19" s="12" t="s">
+      <c r="D19" s="11" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A20" s="13">
+      <c r="A20" s="12">
         <v>16</v>
       </c>
-      <c r="B20" s="12" t="s">
+      <c r="B20" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="C20" s="25" t="s">
+      <c r="C20" s="20" t="s">
         <v>87</v>
       </c>
-      <c r="D20" s="12" t="s">
+      <c r="D20" s="11" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A21" s="13">
+      <c r="A21" s="12">
         <v>17</v>
       </c>
-      <c r="B21" s="12" t="s">
+      <c r="B21" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="C21" s="25" t="s">
+      <c r="C21" s="20" t="s">
         <v>87</v>
       </c>
-      <c r="D21" s="12" t="s">
+      <c r="D21" s="11" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A22" s="13">
+      <c r="A22" s="12">
         <v>18</v>
       </c>
-      <c r="B22" s="12" t="s">
+      <c r="B22" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="C22" s="25" t="s">
+      <c r="C22" s="20" t="s">
         <v>87</v>
       </c>
-      <c r="D22" s="12" t="s">
+      <c r="D22" s="11" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A23" s="9"/>
-      <c r="B23" s="9"/>
-      <c r="C23" s="9"/>
-      <c r="D23" s="9"/>
+      <c r="A23" s="8"/>
+      <c r="B23" s="8"/>
+      <c r="C23" s="8"/>
+      <c r="D23" s="8"/>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A24" s="9"/>
-      <c r="B24" s="9"/>
-      <c r="C24" s="9"/>
-      <c r="D24" s="9"/>
-    </row>
-    <row r="25" spans="1:4" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="A24" s="8"/>
+      <c r="B24" s="8"/>
+      <c r="C24" s="8"/>
+      <c r="D24" s="8"/>
+    </row>
+    <row r="25" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A25" s="1" t="s">
         <v>92</v>
       </c>
@@ -2590,96 +2590,96 @@
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A26" s="9"/>
-      <c r="B26" s="12" t="s">
+      <c r="A26" s="8"/>
+      <c r="B26" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="C26" s="16">
+      <c r="C26" s="15">
         <f>COUNTIF($C$5:$C$22,B26)</f>
         <v>8</v>
       </c>
-      <c r="D26" s="26">
+      <c r="D26" s="21">
         <f>C26/$C$30</f>
         <v>0.44444444444444442</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A27" s="9"/>
-      <c r="B27" s="12" t="s">
+      <c r="A27" s="8"/>
+      <c r="B27" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="C27" s="16">
+      <c r="C27" s="15">
         <f>COUNTIF($C$5:$C$22,B27)</f>
         <v>3</v>
       </c>
-      <c r="D27" s="26">
+      <c r="D27" s="21">
         <f>C27/$C$30</f>
         <v>0.16666666666666666</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A28" s="9"/>
-      <c r="B28" s="12" t="s">
+      <c r="A28" s="8"/>
+      <c r="B28" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="C28" s="16">
+      <c r="C28" s="15">
         <f>COUNTIF($C$5:$C$22,B28)</f>
         <v>3</v>
       </c>
-      <c r="D28" s="26">
+      <c r="D28" s="21">
         <f>C28/$C$30</f>
         <v>0.16666666666666666</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A29" s="9"/>
-      <c r="B29" s="12" t="s">
+      <c r="A29" s="8"/>
+      <c r="B29" s="11" t="s">
         <v>87</v>
       </c>
-      <c r="C29" s="16">
+      <c r="C29" s="15">
         <f>COUNTIF($C$5:$C$22,B29)</f>
         <v>4</v>
       </c>
-      <c r="D29" s="26">
+      <c r="D29" s="21">
         <f>C29/$C$30</f>
         <v>0.22222222222222221</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A30" s="9"/>
-      <c r="B30" s="17" t="s">
+      <c r="A30" s="8"/>
+      <c r="B30" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="C30" s="18">
+      <c r="C30" s="17">
         <f>SUM(C26:C29)</f>
         <v>18</v>
       </c>
-      <c r="D30" s="27">
+      <c r="D30" s="22">
         <f>SUM(D26:D29)</f>
         <v>0.99999999999999989</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A31" s="9"/>
-      <c r="B31" s="17" t="s">
+      <c r="A31" s="8"/>
+      <c r="B31" s="16" t="s">
         <v>96</v>
       </c>
-      <c r="C31" s="27">
+      <c r="C31" s="22">
         <f>C26/C30</f>
         <v>0.44444444444444442</v>
       </c>
-      <c r="D31" s="17"/>
+      <c r="D31" s="16"/>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A32" s="9"/>
-      <c r="B32" s="17" t="s">
+      <c r="A32" s="8"/>
+      <c r="B32" s="16" t="s">
         <v>97</v>
       </c>
-      <c r="C32" s="17" t="str">
+      <c r="C32" s="16" t="str">
         <f>IF(C31&lt;=0.6,"выполнено","не выполнено")</f>
         <v>выполнено</v>
       </c>
-      <c r="D32" s="17"/>
+      <c r="D32" s="16"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="C5:C22">
@@ -2688,7 +2688,7 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" fitToHeight="0" orientation="landscape"/>
   <headerFooter>
     <oddFooter>&amp;C&amp;P / &amp;N</oddFooter>
   </headerFooter>
@@ -2704,35 +2704,35 @@
   <dimension ref="A1:D37"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="8" customWidth="1"/>
-    <col min="2" max="2" width="36" customWidth="1"/>
-    <col min="3" max="3" width="80" customWidth="1"/>
-    <col min="4" max="4" width="14" customWidth="1"/>
+    <col min="1" max="1" width="8" style="29" customWidth="1"/>
+    <col min="2" max="2" width="36" style="29" customWidth="1"/>
+    <col min="3" max="3" width="80" style="29" customWidth="1"/>
+    <col min="4" max="4" width="14" style="29" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="36" customFormat="1" ht="18" x14ac:dyDescent="0.45">
-      <c r="A1" s="24" t="s">
+    <row r="1" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A1" s="19" t="s">
         <v>98</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-    </row>
-    <row r="2" spans="1:4" s="36" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="11" t="s">
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A2" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="B2" s="9"/>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9"/>
+      <c r="B2" s="8"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A3" s="9"/>
-      <c r="B3" s="9"/>
-      <c r="C3" s="9"/>
-      <c r="D3" s="9"/>
-    </row>
-    <row r="4" spans="1:4" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="A3" s="8"/>
+      <c r="B3" s="8"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="8"/>
+    </row>
+    <row r="4" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
         <v>32</v>
       </c>
@@ -2747,345 +2747,345 @@
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A5" s="30" t="s">
+      <c r="A5" s="25" t="s">
         <v>101</v>
       </c>
-      <c r="B5" s="31" t="s">
+      <c r="B5" s="26" t="s">
         <v>102</v>
       </c>
-      <c r="C5" s="31"/>
-      <c r="D5" s="32" t="s">
+      <c r="C5" s="26"/>
+      <c r="D5" s="27" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A6" s="28" t="s">
+    <row r="6" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A6" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="B6" s="12"/>
-      <c r="C6" s="12" t="s">
+      <c r="B6" s="11"/>
+      <c r="C6" s="11" t="s">
         <v>105</v>
       </c>
-      <c r="D6" s="13"/>
-    </row>
-    <row r="7" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A7" s="28" t="s">
+      <c r="D6" s="12"/>
+    </row>
+    <row r="7" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A7" s="23" t="s">
         <v>106</v>
       </c>
-      <c r="B7" s="12"/>
-      <c r="C7" s="12" t="s">
+      <c r="B7" s="11"/>
+      <c r="C7" s="11" t="s">
         <v>107</v>
       </c>
-      <c r="D7" s="13"/>
+      <c r="D7" s="12"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A8" s="28" t="s">
+      <c r="A8" s="23" t="s">
         <v>108</v>
       </c>
-      <c r="B8" s="12"/>
-      <c r="C8" s="12" t="s">
+      <c r="B8" s="11"/>
+      <c r="C8" s="11" t="s">
         <v>109</v>
       </c>
-      <c r="D8" s="13"/>
+      <c r="D8" s="12"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A9" s="28" t="s">
+      <c r="A9" s="23" t="s">
         <v>110</v>
       </c>
-      <c r="B9" s="12"/>
-      <c r="C9" s="12" t="s">
+      <c r="B9" s="11"/>
+      <c r="C9" s="11" t="s">
         <v>111</v>
       </c>
-      <c r="D9" s="13"/>
+      <c r="D9" s="12"/>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A10" s="30" t="s">
+      <c r="A10" s="25" t="s">
         <v>112</v>
       </c>
-      <c r="B10" s="31" t="s">
+      <c r="B10" s="26" t="s">
         <v>113</v>
       </c>
-      <c r="C10" s="31"/>
-      <c r="D10" s="32" t="s">
+      <c r="C10" s="26"/>
+      <c r="D10" s="27" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A11" s="28" t="s">
+    <row r="11" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A11" s="23" t="s">
         <v>115</v>
       </c>
-      <c r="B11" s="12"/>
-      <c r="C11" s="12" t="s">
+      <c r="B11" s="11"/>
+      <c r="C11" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="D11" s="13"/>
+      <c r="D11" s="12"/>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A12" s="28" t="s">
+      <c r="A12" s="23" t="s">
         <v>117</v>
       </c>
-      <c r="B12" s="12"/>
-      <c r="C12" s="12" t="s">
+      <c r="B12" s="11"/>
+      <c r="C12" s="11" t="s">
         <v>118</v>
       </c>
-      <c r="D12" s="13"/>
+      <c r="D12" s="12"/>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A13" s="28" t="s">
+      <c r="A13" s="23" t="s">
         <v>119</v>
       </c>
-      <c r="B13" s="12"/>
-      <c r="C13" s="12" t="s">
+      <c r="B13" s="11"/>
+      <c r="C13" s="11" t="s">
         <v>120</v>
       </c>
-      <c r="D13" s="13"/>
+      <c r="D13" s="12"/>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A14" s="28" t="s">
+      <c r="A14" s="23" t="s">
         <v>121</v>
       </c>
-      <c r="B14" s="12"/>
-      <c r="C14" s="12" t="s">
+      <c r="B14" s="11"/>
+      <c r="C14" s="11" t="s">
         <v>122</v>
       </c>
-      <c r="D14" s="13"/>
+      <c r="D14" s="12"/>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A15" s="30" t="s">
+      <c r="A15" s="25" t="s">
         <v>123</v>
       </c>
-      <c r="B15" s="31" t="s">
+      <c r="B15" s="26" t="s">
         <v>124</v>
       </c>
-      <c r="C15" s="31"/>
-      <c r="D15" s="32" t="s">
+      <c r="C15" s="26"/>
+      <c r="D15" s="27" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A16" s="28" t="s">
+      <c r="A16" s="23" t="s">
         <v>126</v>
       </c>
-      <c r="B16" s="12"/>
-      <c r="C16" s="12" t="s">
+      <c r="B16" s="11"/>
+      <c r="C16" s="11" t="s">
         <v>127</v>
       </c>
-      <c r="D16" s="13"/>
+      <c r="D16" s="12"/>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A17" s="28" t="s">
+      <c r="A17" s="23" t="s">
         <v>128</v>
       </c>
-      <c r="B17" s="12"/>
-      <c r="C17" s="12" t="s">
+      <c r="B17" s="11"/>
+      <c r="C17" s="11" t="s">
         <v>129</v>
       </c>
-      <c r="D17" s="13"/>
+      <c r="D17" s="12"/>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A18" s="28" t="s">
+      <c r="A18" s="23" t="s">
         <v>130</v>
       </c>
-      <c r="B18" s="12"/>
-      <c r="C18" s="12" t="s">
+      <c r="B18" s="11"/>
+      <c r="C18" s="11" t="s">
         <v>131</v>
       </c>
-      <c r="D18" s="13"/>
+      <c r="D18" s="12"/>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A19" s="28" t="s">
+      <c r="A19" s="23" t="s">
         <v>132</v>
       </c>
-      <c r="B19" s="12"/>
-      <c r="C19" s="12" t="s">
+      <c r="B19" s="11"/>
+      <c r="C19" s="11" t="s">
         <v>133</v>
       </c>
-      <c r="D19" s="13"/>
+      <c r="D19" s="12"/>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A20" s="28" t="s">
+      <c r="A20" s="23" t="s">
         <v>134</v>
       </c>
-      <c r="B20" s="12"/>
-      <c r="C20" s="12" t="s">
+      <c r="B20" s="11"/>
+      <c r="C20" s="11" t="s">
         <v>135</v>
       </c>
-      <c r="D20" s="13"/>
+      <c r="D20" s="12"/>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A21" s="30" t="s">
+      <c r="A21" s="25" t="s">
         <v>136</v>
       </c>
-      <c r="B21" s="31" t="s">
+      <c r="B21" s="26" t="s">
         <v>137</v>
       </c>
-      <c r="C21" s="31"/>
-      <c r="D21" s="32" t="s">
+      <c r="C21" s="26"/>
+      <c r="D21" s="27" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A22" s="28" t="s">
+      <c r="A22" s="23" t="s">
         <v>139</v>
       </c>
-      <c r="B22" s="12"/>
-      <c r="C22" s="12" t="s">
+      <c r="B22" s="11"/>
+      <c r="C22" s="11" t="s">
         <v>140</v>
       </c>
-      <c r="D22" s="13"/>
-    </row>
-    <row r="23" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A23" s="28" t="s">
+      <c r="D22" s="12"/>
+    </row>
+    <row r="23" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A23" s="23" t="s">
         <v>141</v>
       </c>
-      <c r="B23" s="12"/>
-      <c r="C23" s="12" t="s">
+      <c r="B23" s="11"/>
+      <c r="C23" s="11" t="s">
         <v>142</v>
       </c>
-      <c r="D23" s="13"/>
+      <c r="D23" s="12"/>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A24" s="28" t="s">
+      <c r="A24" s="23" t="s">
         <v>143</v>
       </c>
-      <c r="B24" s="12"/>
-      <c r="C24" s="12" t="s">
+      <c r="B24" s="11"/>
+      <c r="C24" s="11" t="s">
         <v>144</v>
       </c>
-      <c r="D24" s="13"/>
+      <c r="D24" s="12"/>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A25" s="30" t="s">
+      <c r="A25" s="25" t="s">
         <v>145</v>
       </c>
-      <c r="B25" s="31" t="s">
+      <c r="B25" s="26" t="s">
         <v>146</v>
       </c>
-      <c r="C25" s="31"/>
-      <c r="D25" s="32" t="s">
+      <c r="C25" s="26"/>
+      <c r="D25" s="27" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A26" s="28" t="s">
+      <c r="A26" s="23" t="s">
         <v>148</v>
       </c>
-      <c r="B26" s="12"/>
-      <c r="C26" s="12" t="s">
+      <c r="B26" s="11"/>
+      <c r="C26" s="11" t="s">
         <v>149</v>
       </c>
-      <c r="D26" s="13"/>
-    </row>
-    <row r="27" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A27" s="28" t="s">
+      <c r="D26" s="12"/>
+    </row>
+    <row r="27" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A27" s="23" t="s">
         <v>150</v>
       </c>
-      <c r="B27" s="12"/>
-      <c r="C27" s="12" t="s">
+      <c r="B27" s="11"/>
+      <c r="C27" s="11" t="s">
         <v>151</v>
       </c>
-      <c r="D27" s="13"/>
+      <c r="D27" s="12"/>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A28" s="28" t="s">
+      <c r="A28" s="23" t="s">
         <v>152</v>
       </c>
-      <c r="B28" s="12"/>
-      <c r="C28" s="12" t="s">
+      <c r="B28" s="11"/>
+      <c r="C28" s="11" t="s">
         <v>153</v>
       </c>
-      <c r="D28" s="13"/>
+      <c r="D28" s="12"/>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A29" s="30" t="s">
+      <c r="A29" s="25" t="s">
         <v>154</v>
       </c>
-      <c r="B29" s="31" t="s">
+      <c r="B29" s="26" t="s">
         <v>155</v>
       </c>
-      <c r="C29" s="31"/>
-      <c r="D29" s="32" t="s">
+      <c r="C29" s="26"/>
+      <c r="D29" s="27" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="30" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A30" s="28" t="s">
+    <row r="30" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A30" s="23" t="s">
         <v>157</v>
       </c>
-      <c r="B30" s="12"/>
-      <c r="C30" s="12" t="s">
+      <c r="B30" s="11"/>
+      <c r="C30" s="11" t="s">
         <v>158</v>
       </c>
-      <c r="D30" s="13"/>
+      <c r="D30" s="12"/>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A31" s="28" t="s">
+      <c r="A31" s="23" t="s">
         <v>159</v>
       </c>
-      <c r="B31" s="12"/>
-      <c r="C31" s="12" t="s">
+      <c r="B31" s="11"/>
+      <c r="C31" s="11" t="s">
         <v>160</v>
       </c>
-      <c r="D31" s="13"/>
+      <c r="D31" s="12"/>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A32" s="28" t="s">
+      <c r="A32" s="23" t="s">
         <v>161</v>
       </c>
-      <c r="B32" s="12"/>
-      <c r="C32" s="12" t="s">
+      <c r="B32" s="11"/>
+      <c r="C32" s="11" t="s">
         <v>162</v>
       </c>
-      <c r="D32" s="13"/>
+      <c r="D32" s="12"/>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A33" s="28" t="s">
+      <c r="A33" s="23" t="s">
         <v>163</v>
       </c>
-      <c r="B33" s="12"/>
-      <c r="C33" s="12" t="s">
+      <c r="B33" s="11"/>
+      <c r="C33" s="11" t="s">
         <v>164</v>
       </c>
-      <c r="D33" s="13"/>
+      <c r="D33" s="12"/>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A34" s="9"/>
-      <c r="B34" s="9"/>
-      <c r="C34" s="9"/>
-      <c r="D34" s="9"/>
+      <c r="A34" s="8"/>
+      <c r="B34" s="8"/>
+      <c r="C34" s="8"/>
+      <c r="D34" s="8"/>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A35" s="9"/>
-      <c r="B35" s="17" t="s">
+      <c r="A35" s="8"/>
+      <c r="B35" s="16" t="s">
         <v>165</v>
       </c>
-      <c r="C35" s="29">
+      <c r="C35" s="24">
         <f>COUNTA(B5:B33)</f>
         <v>6</v>
       </c>
-      <c r="D35" s="9"/>
+      <c r="D35" s="8"/>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A36" s="9"/>
-      <c r="B36" s="17" t="s">
+      <c r="A36" s="8"/>
+      <c r="B36" s="16" t="s">
         <v>166</v>
       </c>
-      <c r="C36" s="29">
+      <c r="C36" s="24">
         <f>COUNTA(C5:C33)</f>
         <v>23</v>
       </c>
-      <c r="D36" s="9"/>
-    </row>
-    <row r="37" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A37" s="9"/>
-      <c r="B37" s="17" t="s">
+      <c r="D36" s="8"/>
+    </row>
+    <row r="37" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A37" s="8"/>
+      <c r="B37" s="16" t="s">
         <v>167</v>
       </c>
-      <c r="C37" s="29" t="str">
+      <c r="C37" s="24" t="str">
         <f>IF(AND(C35&gt;=5,C35&lt;=7,C36&gt;=15,C36&lt;=25),"выполнено","не выполнено")</f>
         <v>выполнено</v>
       </c>
-      <c r="D37" s="9"/>
+      <c r="D37" s="8"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A5:D33">
@@ -3094,7 +3094,7 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" scale="94" fitToHeight="0" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="94" fitToHeight="0" orientation="landscape"/>
   <headerFooter>
     <oddFooter>&amp;C&amp;P / &amp;N</oddFooter>
   </headerFooter>
@@ -3110,45 +3110,45 @@
   <dimension ref="A1:G25"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="8" customWidth="1"/>
-    <col min="2" max="2" width="70" customWidth="1"/>
-    <col min="3" max="4" width="13" customWidth="1"/>
-    <col min="5" max="6" width="14" customWidth="1"/>
-    <col min="7" max="7" width="13" customWidth="1"/>
+    <col min="1" max="1" width="8" style="29" customWidth="1"/>
+    <col min="2" max="2" width="70" style="29" customWidth="1"/>
+    <col min="3" max="4" width="13" style="29" customWidth="1"/>
+    <col min="5" max="6" width="14" style="29" customWidth="1"/>
+    <col min="7" max="7" width="13" style="29" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="36" customFormat="1" ht="18" x14ac:dyDescent="0.45">
-      <c r="A1" s="24" t="s">
+    <row r="1" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A1" s="19" t="s">
         <v>168</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-    </row>
-    <row r="2" spans="1:7" s="36" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="11" t="s">
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A2" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="B2" s="9"/>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9"/>
-      <c r="G2" s="9"/>
+      <c r="B2" s="8"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="8"/>
+      <c r="F2" s="8"/>
+      <c r="G2" s="8"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A3" s="9"/>
-      <c r="B3" s="9"/>
-      <c r="C3" s="9"/>
-      <c r="D3" s="9"/>
-      <c r="E3" s="9"/>
-      <c r="F3" s="9"/>
-      <c r="G3" s="9"/>
-    </row>
-    <row r="4" spans="1:7" ht="47.25" x14ac:dyDescent="0.45">
+      <c r="A3" s="8"/>
+      <c r="B3" s="8"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="8"/>
+      <c r="F3" s="8"/>
+      <c r="G3" s="8"/>
+    </row>
+    <row r="4" spans="1:7" ht="47.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
         <v>169</v>
       </c>
@@ -3172,442 +3172,442 @@
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A5" s="28" t="s">
+      <c r="A5" s="23" t="s">
         <v>175</v>
       </c>
-      <c r="B5" s="12" t="s">
+      <c r="B5" s="11" t="s">
         <v>176</v>
       </c>
-      <c r="C5" s="33">
+      <c r="C5" s="35">
         <v>46296</v>
       </c>
-      <c r="D5" s="33">
+      <c r="D5" s="35">
         <v>46326</v>
       </c>
-      <c r="E5" s="13">
+      <c r="E5" s="12">
         <f t="shared" ref="E5:E19" si="0">DATEDIF(C5,D5+1,"m")</f>
         <v>1</v>
       </c>
-      <c r="F5" s="13">
+      <c r="F5" s="12">
         <v>1</v>
       </c>
-      <c r="G5" s="13" t="s">
+      <c r="G5" s="12" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A6" s="28" t="s">
+      <c r="A6" s="23" t="s">
         <v>178</v>
       </c>
-      <c r="B6" s="12" t="s">
+      <c r="B6" s="11" t="s">
         <v>179</v>
       </c>
-      <c r="C6" s="33">
+      <c r="C6" s="35">
         <v>46327</v>
       </c>
-      <c r="D6" s="33">
+      <c r="D6" s="35">
         <v>46356</v>
       </c>
-      <c r="E6" s="13">
+      <c r="E6" s="12">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="F6" s="13">
+      <c r="F6" s="12">
         <v>1</v>
       </c>
-      <c r="G6" s="13" t="s">
+      <c r="G6" s="12" t="s">
         <v>180</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A7" s="28" t="s">
+      <c r="A7" s="23" t="s">
         <v>181</v>
       </c>
-      <c r="B7" s="12" t="s">
+      <c r="B7" s="11" t="s">
         <v>182</v>
       </c>
-      <c r="C7" s="33">
+      <c r="C7" s="35">
         <v>46327</v>
       </c>
-      <c r="D7" s="33">
+      <c r="D7" s="35">
         <v>46356</v>
       </c>
-      <c r="E7" s="13">
+      <c r="E7" s="12">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="F7" s="13">
+      <c r="F7" s="12">
         <v>2</v>
       </c>
-      <c r="G7" s="13" t="s">
+      <c r="G7" s="12" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A8" s="28" t="s">
+      <c r="A8" s="23" t="s">
         <v>183</v>
       </c>
-      <c r="B8" s="12" t="s">
+      <c r="B8" s="11" t="s">
         <v>184</v>
       </c>
-      <c r="C8" s="33">
+      <c r="C8" s="35">
         <v>46327</v>
       </c>
-      <c r="D8" s="33">
+      <c r="D8" s="35">
         <v>46356</v>
       </c>
-      <c r="E8" s="13">
+      <c r="E8" s="12">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="F8" s="13">
+      <c r="F8" s="12">
         <v>2</v>
       </c>
-      <c r="G8" s="13" t="s">
+      <c r="G8" s="12" t="s">
         <v>180</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A9" s="28" t="s">
+      <c r="A9" s="23" t="s">
         <v>185</v>
       </c>
-      <c r="B9" s="12" t="s">
+      <c r="B9" s="11" t="s">
         <v>186</v>
       </c>
-      <c r="C9" s="33">
+      <c r="C9" s="35">
         <v>46327</v>
       </c>
-      <c r="D9" s="33">
+      <c r="D9" s="35">
         <v>46387</v>
       </c>
-      <c r="E9" s="13">
+      <c r="E9" s="12">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="F9" s="13">
+      <c r="F9" s="12">
         <v>2</v>
       </c>
-      <c r="G9" s="13" t="s">
+      <c r="G9" s="12" t="s">
         <v>180</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A10" s="28" t="s">
+      <c r="A10" s="23" t="s">
         <v>187</v>
       </c>
-      <c r="B10" s="12" t="s">
+      <c r="B10" s="11" t="s">
         <v>188</v>
       </c>
-      <c r="C10" s="33">
+      <c r="C10" s="35">
         <v>46357</v>
       </c>
-      <c r="D10" s="33">
+      <c r="D10" s="35">
         <v>46446</v>
       </c>
-      <c r="E10" s="13">
+      <c r="E10" s="12">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="F10" s="13">
+      <c r="F10" s="12">
         <v>3</v>
       </c>
-      <c r="G10" s="13" t="s">
+      <c r="G10" s="12" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A11" s="28" t="s">
+      <c r="A11" s="23" t="s">
         <v>189</v>
       </c>
-      <c r="B11" s="12" t="s">
+      <c r="B11" s="11" t="s">
         <v>190</v>
       </c>
-      <c r="C11" s="33">
+      <c r="C11" s="35">
         <v>46357</v>
       </c>
-      <c r="D11" s="33">
+      <c r="D11" s="35">
         <v>46418</v>
       </c>
-      <c r="E11" s="13">
+      <c r="E11" s="12">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="F11" s="13">
+      <c r="F11" s="12">
         <v>3</v>
       </c>
-      <c r="G11" s="13" t="s">
+      <c r="G11" s="12" t="s">
         <v>180</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A12" s="28" t="s">
+      <c r="A12" s="23" t="s">
         <v>191</v>
       </c>
-      <c r="B12" s="12" t="s">
+      <c r="B12" s="11" t="s">
         <v>192</v>
       </c>
-      <c r="C12" s="33">
+      <c r="C12" s="35">
         <v>46357</v>
       </c>
-      <c r="D12" s="33">
+      <c r="D12" s="35">
         <v>46418</v>
       </c>
-      <c r="E12" s="13">
+      <c r="E12" s="12">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="F12" s="13">
+      <c r="F12" s="12">
         <v>3</v>
       </c>
-      <c r="G12" s="13" t="s">
+      <c r="G12" s="12" t="s">
         <v>180</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A13" s="28" t="s">
+      <c r="A13" s="23" t="s">
         <v>193</v>
       </c>
-      <c r="B13" s="12" t="s">
+      <c r="B13" s="11" t="s">
         <v>194</v>
       </c>
-      <c r="C13" s="33">
+      <c r="C13" s="35">
         <v>46447</v>
       </c>
-      <c r="D13" s="33">
+      <c r="D13" s="35">
         <v>46477</v>
       </c>
-      <c r="E13" s="13">
+      <c r="E13" s="12">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="F13" s="13">
+      <c r="F13" s="12">
         <v>3</v>
       </c>
-      <c r="G13" s="13" t="s">
+      <c r="G13" s="12" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A14" s="28" t="s">
+      <c r="A14" s="23" t="s">
         <v>195</v>
       </c>
-      <c r="B14" s="12" t="s">
+      <c r="B14" s="11" t="s">
         <v>196</v>
       </c>
-      <c r="C14" s="33">
+      <c r="C14" s="35">
         <v>46478</v>
       </c>
-      <c r="D14" s="33">
+      <c r="D14" s="35">
         <v>46538</v>
       </c>
-      <c r="E14" s="13">
+      <c r="E14" s="12">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="F14" s="13">
+      <c r="F14" s="12">
         <v>4</v>
       </c>
-      <c r="G14" s="13" t="s">
+      <c r="G14" s="12" t="s">
         <v>180</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A15" s="28" t="s">
+      <c r="A15" s="23" t="s">
         <v>197</v>
       </c>
-      <c r="B15" s="12" t="s">
+      <c r="B15" s="11" t="s">
         <v>198</v>
       </c>
-      <c r="C15" s="33">
+      <c r="C15" s="35">
         <v>46478</v>
       </c>
-      <c r="D15" s="33">
+      <c r="D15" s="35">
         <v>46507</v>
       </c>
-      <c r="E15" s="13">
+      <c r="E15" s="12">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="F15" s="13">
+      <c r="F15" s="12">
         <v>4</v>
       </c>
-      <c r="G15" s="13" t="s">
+      <c r="G15" s="12" t="s">
         <v>180</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A16" s="28" t="s">
+      <c r="A16" s="23" t="s">
         <v>147</v>
       </c>
-      <c r="B16" s="12" t="s">
+      <c r="B16" s="11" t="s">
         <v>199</v>
       </c>
-      <c r="C16" s="33">
+      <c r="C16" s="35">
         <v>46478</v>
       </c>
-      <c r="D16" s="33">
+      <c r="D16" s="35">
         <v>46568</v>
       </c>
-      <c r="E16" s="13">
+      <c r="E16" s="12">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="F16" s="13">
+      <c r="F16" s="12">
         <v>5</v>
       </c>
-      <c r="G16" s="13" t="s">
+      <c r="G16" s="12" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A17" s="28" t="s">
+      <c r="A17" s="23" t="s">
         <v>200</v>
       </c>
-      <c r="B17" s="12" t="s">
+      <c r="B17" s="11" t="s">
         <v>201</v>
       </c>
-      <c r="C17" s="33">
+      <c r="C17" s="35">
         <v>46569</v>
       </c>
-      <c r="D17" s="33">
+      <c r="D17" s="35">
         <v>46599</v>
       </c>
-      <c r="E17" s="13">
+      <c r="E17" s="12">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="F17" s="13">
+      <c r="F17" s="12">
         <v>6</v>
       </c>
-      <c r="G17" s="13" t="s">
+      <c r="G17" s="12" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A18" s="28" t="s">
+      <c r="A18" s="23" t="s">
         <v>202</v>
       </c>
-      <c r="B18" s="12" t="s">
+      <c r="B18" s="11" t="s">
         <v>203</v>
       </c>
-      <c r="C18" s="33">
+      <c r="C18" s="35">
         <v>46600</v>
       </c>
-      <c r="D18" s="33">
+      <c r="D18" s="35">
         <v>46630</v>
       </c>
-      <c r="E18" s="13">
+      <c r="E18" s="12">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="F18" s="13">
+      <c r="F18" s="12">
         <v>6</v>
       </c>
-      <c r="G18" s="13" t="s">
+      <c r="G18" s="12" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A19" s="28" t="s">
+      <c r="A19" s="23" t="s">
         <v>204</v>
       </c>
-      <c r="B19" s="12" t="s">
+      <c r="B19" s="11" t="s">
         <v>205</v>
       </c>
-      <c r="C19" s="33">
+      <c r="C19" s="35">
         <v>46631</v>
       </c>
-      <c r="D19" s="33">
+      <c r="D19" s="35">
         <v>46660</v>
       </c>
-      <c r="E19" s="13">
+      <c r="E19" s="12">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="F19" s="13">
+      <c r="F19" s="12">
         <v>6</v>
       </c>
-      <c r="G19" s="13" t="s">
+      <c r="G19" s="12" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A20" s="9"/>
-      <c r="B20" s="9"/>
-      <c r="C20" s="9"/>
-      <c r="D20" s="9"/>
-      <c r="E20" s="9"/>
-      <c r="F20" s="9"/>
-      <c r="G20" s="9"/>
+      <c r="A20" s="8"/>
+      <c r="B20" s="8"/>
+      <c r="C20" s="8"/>
+      <c r="D20" s="8"/>
+      <c r="E20" s="8"/>
+      <c r="F20" s="8"/>
+      <c r="G20" s="8"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A21" s="9"/>
-      <c r="B21" s="17" t="s">
+      <c r="A21" s="8"/>
+      <c r="B21" s="16" t="s">
         <v>206</v>
       </c>
-      <c r="C21" s="34">
+      <c r="C21" s="36">
         <f>MIN(C5:C19)</f>
         <v>46296</v>
       </c>
-      <c r="D21" s="9"/>
-      <c r="E21" s="9"/>
-      <c r="F21" s="9"/>
-      <c r="G21" s="9"/>
+      <c r="D21" s="8"/>
+      <c r="E21" s="8"/>
+      <c r="F21" s="8"/>
+      <c r="G21" s="8"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A22" s="9"/>
-      <c r="B22" s="17" t="s">
+      <c r="A22" s="8"/>
+      <c r="B22" s="16" t="s">
         <v>207</v>
       </c>
-      <c r="C22" s="34">
+      <c r="C22" s="36">
         <f>MAX(D5:D19)</f>
         <v>46660</v>
       </c>
-      <c r="D22" s="9"/>
-      <c r="E22" s="9"/>
-      <c r="F22" s="9"/>
-      <c r="G22" s="9"/>
+      <c r="D22" s="8"/>
+      <c r="E22" s="8"/>
+      <c r="F22" s="8"/>
+      <c r="G22" s="8"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A23" s="9"/>
-      <c r="B23" s="17" t="s">
+      <c r="A23" s="8"/>
+      <c r="B23" s="16" t="s">
         <v>208</v>
       </c>
-      <c r="C23" s="18">
+      <c r="C23" s="17">
         <f>DATEDIF(C21,C22+1,"m")</f>
         <v>12</v>
       </c>
-      <c r="D23" s="9"/>
-      <c r="E23" s="9"/>
-      <c r="F23" s="9"/>
-      <c r="G23" s="9"/>
+      <c r="D23" s="8"/>
+      <c r="E23" s="8"/>
+      <c r="F23" s="8"/>
+      <c r="G23" s="8"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A24" s="9"/>
-      <c r="B24" s="17" t="s">
+      <c r="A24" s="8"/>
+      <c r="B24" s="16" t="s">
         <v>209</v>
       </c>
-      <c r="C24" s="18">
+      <c r="C24" s="17">
         <f>SUMIF(G5:G19,"да",E5:E19)</f>
         <v>12</v>
       </c>
-      <c r="D24" s="9"/>
-      <c r="E24" s="9"/>
-      <c r="F24" s="9"/>
-      <c r="G24" s="9"/>
-    </row>
-    <row r="25" spans="1:7" ht="57" x14ac:dyDescent="0.45">
-      <c r="A25" s="9"/>
-      <c r="B25" s="17" t="s">
+      <c r="D24" s="8"/>
+      <c r="E24" s="8"/>
+      <c r="F24" s="8"/>
+      <c r="G24" s="8"/>
+    </row>
+    <row r="25" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A25" s="8"/>
+      <c r="B25" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="C25" s="17" t="s">
+      <c r="C25" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="D25" s="9"/>
-      <c r="E25" s="9"/>
-      <c r="F25" s="9"/>
-      <c r="G25" s="9"/>
+      <c r="D25" s="8"/>
+      <c r="E25" s="8"/>
+      <c r="F25" s="8"/>
+      <c r="G25" s="8"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A5:B19">
@@ -3621,7 +3621,7 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" scale="89" fitToHeight="0" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="89" fitToHeight="0" orientation="landscape"/>
   <headerFooter>
     <oddFooter>&amp;C&amp;P / &amp;N</oddFooter>
   </headerFooter>
@@ -3637,50 +3637,50 @@
   <dimension ref="A1:H25"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="10" customWidth="1"/>
-    <col min="2" max="2" width="46" customWidth="1"/>
-    <col min="3" max="3" width="32" customWidth="1"/>
-    <col min="4" max="5" width="12" customWidth="1"/>
-    <col min="6" max="6" width="11" customWidth="1"/>
-    <col min="7" max="7" width="30" customWidth="1"/>
-    <col min="8" max="8" width="55" customWidth="1"/>
+    <col min="1" max="1" width="10" style="29" customWidth="1"/>
+    <col min="2" max="2" width="46" style="29" customWidth="1"/>
+    <col min="3" max="3" width="32" style="29" customWidth="1"/>
+    <col min="4" max="5" width="12" style="29" customWidth="1"/>
+    <col min="6" max="6" width="11" style="29" customWidth="1"/>
+    <col min="7" max="7" width="30" style="29" customWidth="1"/>
+    <col min="8" max="8" width="55" style="29" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="36" customFormat="1" ht="18" x14ac:dyDescent="0.45">
-      <c r="A1" s="24" t="s">
+    <row r="1" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A1" s="19" t="s">
         <v>210</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
-    </row>
-    <row r="2" spans="1:8" s="36" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="11" t="s">
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="8"/>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A2" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="B2" s="9"/>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9"/>
-      <c r="G2" s="9"/>
-      <c r="H2" s="9"/>
+      <c r="B2" s="8"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="8"/>
+      <c r="F2" s="8"/>
+      <c r="G2" s="8"/>
+      <c r="H2" s="8"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A3" s="9"/>
-      <c r="B3" s="9"/>
-      <c r="C3" s="9"/>
-      <c r="D3" s="9"/>
-      <c r="E3" s="9"/>
-      <c r="F3" s="9"/>
-      <c r="G3" s="9"/>
-      <c r="H3" s="9"/>
-    </row>
-    <row r="4" spans="1:8" ht="31.5" x14ac:dyDescent="0.45">
+      <c r="A3" s="8"/>
+      <c r="B3" s="8"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="8"/>
+      <c r="F3" s="8"/>
+      <c r="G3" s="8"/>
+      <c r="H3" s="8"/>
+    </row>
+    <row r="4" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
         <v>32</v>
       </c>
@@ -3706,391 +3706,391 @@
         <v>217</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A5" s="13">
+    <row r="5" spans="1:8" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A5" s="12">
         <v>1</v>
       </c>
-      <c r="B5" s="12" t="s">
+      <c r="B5" s="11" t="s">
         <v>218</v>
       </c>
-      <c r="C5" s="13" t="s">
+      <c r="C5" s="12" t="s">
         <v>219</v>
       </c>
-      <c r="D5" s="14">
+      <c r="D5" s="13">
         <v>5</v>
       </c>
-      <c r="E5" s="14">
+      <c r="E5" s="13">
         <v>5</v>
       </c>
-      <c r="F5" s="32" t="str">
+      <c r="F5" s="27" t="str">
         <f t="shared" ref="F5:F17" si="0">IF(E5&gt;=4,IF(D5&gt;=3,"A","D"),IF(D5&gt;=3,"B","C"))</f>
         <v>A</v>
       </c>
-      <c r="G5" s="12" t="str">
+      <c r="G5" s="11" t="str">
         <f t="shared" ref="G5:G17" si="1">VLOOKUP(F5,$A$21:$B$24,2,FALSE)</f>
         <v>Активное вовлечение</v>
       </c>
-      <c r="H5" s="12" t="s">
+      <c r="H5" s="11" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A6" s="13">
+    <row r="6" spans="1:8" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A6" s="12">
         <v>2</v>
       </c>
-      <c r="B6" s="12" t="s">
+      <c r="B6" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="C6" s="13" t="s">
+      <c r="C6" s="12" t="s">
         <v>219</v>
       </c>
-      <c r="D6" s="14">
+      <c r="D6" s="13">
         <v>5</v>
       </c>
-      <c r="E6" s="14">
+      <c r="E6" s="13">
         <v>4</v>
       </c>
-      <c r="F6" s="32" t="str">
+      <c r="F6" s="27" t="str">
         <f t="shared" si="0"/>
         <v>A</v>
       </c>
-      <c r="G6" s="12" t="str">
+      <c r="G6" s="11" t="str">
         <f t="shared" si="1"/>
         <v>Активное вовлечение</v>
       </c>
-      <c r="H6" s="12" t="s">
+      <c r="H6" s="11" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A7" s="13">
+    <row r="7" spans="1:8" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A7" s="12">
         <v>3</v>
       </c>
-      <c r="B7" s="12" t="s">
+      <c r="B7" s="11" t="s">
         <v>222</v>
       </c>
-      <c r="C7" s="13" t="s">
+      <c r="C7" s="12" t="s">
         <v>219</v>
       </c>
-      <c r="D7" s="14">
+      <c r="D7" s="13">
         <v>4</v>
       </c>
-      <c r="E7" s="14">
+      <c r="E7" s="13">
         <v>3</v>
       </c>
-      <c r="F7" s="32" t="str">
+      <c r="F7" s="27" t="str">
         <f t="shared" si="0"/>
         <v>B</v>
       </c>
-      <c r="G7" s="12" t="str">
+      <c r="G7" s="11" t="str">
         <f t="shared" si="1"/>
         <v>Консультирование</v>
       </c>
-      <c r="H7" s="12" t="s">
+      <c r="H7" s="11" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A8" s="13">
+    <row r="8" spans="1:8" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A8" s="12">
         <v>4</v>
       </c>
-      <c r="B8" s="12" t="s">
+      <c r="B8" s="11" t="s">
         <v>224</v>
       </c>
-      <c r="C8" s="13" t="s">
+      <c r="C8" s="12" t="s">
         <v>225</v>
       </c>
-      <c r="D8" s="14">
+      <c r="D8" s="13">
         <v>5</v>
       </c>
-      <c r="E8" s="14">
+      <c r="E8" s="13">
         <v>3</v>
       </c>
-      <c r="F8" s="32" t="str">
+      <c r="F8" s="27" t="str">
         <f t="shared" si="0"/>
         <v>B</v>
       </c>
-      <c r="G8" s="12" t="str">
+      <c r="G8" s="11" t="str">
         <f t="shared" si="1"/>
         <v>Консультирование</v>
       </c>
-      <c r="H8" s="12" t="s">
+      <c r="H8" s="11" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A9" s="13">
+    <row r="9" spans="1:8" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A9" s="12">
         <v>5</v>
       </c>
-      <c r="B9" s="12" t="s">
+      <c r="B9" s="11" t="s">
         <v>227</v>
       </c>
-      <c r="C9" s="13" t="s">
+      <c r="C9" s="12" t="s">
         <v>225</v>
       </c>
-      <c r="D9" s="14">
+      <c r="D9" s="13">
         <v>4</v>
       </c>
-      <c r="E9" s="14">
+      <c r="E9" s="13">
         <v>3</v>
       </c>
-      <c r="F9" s="32" t="str">
+      <c r="F9" s="27" t="str">
         <f t="shared" si="0"/>
         <v>B</v>
       </c>
-      <c r="G9" s="12" t="str">
+      <c r="G9" s="11" t="str">
         <f t="shared" si="1"/>
         <v>Консультирование</v>
       </c>
-      <c r="H9" s="12" t="s">
+      <c r="H9" s="11" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A10" s="13">
+    <row r="10" spans="1:8" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A10" s="12">
         <v>6</v>
       </c>
-      <c r="B10" s="12" t="s">
+      <c r="B10" s="11" t="s">
         <v>229</v>
       </c>
-      <c r="C10" s="13" t="s">
+      <c r="C10" s="12" t="s">
         <v>225</v>
       </c>
-      <c r="D10" s="14">
+      <c r="D10" s="13">
         <v>1</v>
       </c>
-      <c r="E10" s="14">
+      <c r="E10" s="13">
         <v>4</v>
       </c>
-      <c r="F10" s="32" t="str">
+      <c r="F10" s="27" t="str">
         <f t="shared" si="0"/>
         <v>D</v>
       </c>
-      <c r="G10" s="12" t="str">
+      <c r="G10" s="11" t="str">
         <f t="shared" si="1"/>
         <v>Минимальное информирование</v>
       </c>
-      <c r="H10" s="12" t="s">
+      <c r="H10" s="11" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A11" s="13">
+    <row r="11" spans="1:8" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A11" s="12">
         <v>7</v>
       </c>
-      <c r="B11" s="12" t="s">
+      <c r="B11" s="11" t="s">
         <v>231</v>
       </c>
-      <c r="C11" s="13" t="s">
+      <c r="C11" s="12" t="s">
         <v>225</v>
       </c>
-      <c r="D11" s="14">
+      <c r="D11" s="13">
         <v>1</v>
       </c>
-      <c r="E11" s="14">
+      <c r="E11" s="13">
         <v>5</v>
       </c>
-      <c r="F11" s="32" t="str">
+      <c r="F11" s="27" t="str">
         <f t="shared" si="0"/>
         <v>D</v>
       </c>
-      <c r="G11" s="12" t="str">
+      <c r="G11" s="11" t="str">
         <f t="shared" si="1"/>
         <v>Минимальное информирование</v>
       </c>
-      <c r="H11" s="12" t="s">
+      <c r="H11" s="11" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A12" s="13">
+    <row r="12" spans="1:8" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A12" s="12">
         <v>8</v>
       </c>
-      <c r="B12" s="12" t="s">
+      <c r="B12" s="11" t="s">
         <v>233</v>
       </c>
-      <c r="C12" s="13" t="s">
+      <c r="C12" s="12" t="s">
         <v>225</v>
       </c>
-      <c r="D12" s="14">
+      <c r="D12" s="13">
         <v>2</v>
       </c>
-      <c r="E12" s="14">
+      <c r="E12" s="13">
         <v>4</v>
       </c>
-      <c r="F12" s="32" t="str">
+      <c r="F12" s="27" t="str">
         <f t="shared" si="0"/>
         <v>D</v>
       </c>
-      <c r="G12" s="12" t="str">
+      <c r="G12" s="11" t="str">
         <f t="shared" si="1"/>
         <v>Минимальное информирование</v>
       </c>
-      <c r="H12" s="12" t="s">
+      <c r="H12" s="11" t="s">
         <v>234</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A13" s="13">
+      <c r="A13" s="12">
         <v>9</v>
       </c>
-      <c r="B13" s="12" t="s">
+      <c r="B13" s="11" t="s">
         <v>235</v>
       </c>
-      <c r="C13" s="13" t="s">
+      <c r="C13" s="12" t="s">
         <v>225</v>
       </c>
-      <c r="D13" s="14">
+      <c r="D13" s="13">
         <v>2</v>
       </c>
-      <c r="E13" s="14">
+      <c r="E13" s="13">
         <v>2</v>
       </c>
-      <c r="F13" s="32" t="str">
+      <c r="F13" s="27" t="str">
         <f t="shared" si="0"/>
         <v>C</v>
       </c>
-      <c r="G13" s="12" t="str">
+      <c r="G13" s="11" t="str">
         <f t="shared" si="1"/>
         <v>Минимальный контроль</v>
       </c>
-      <c r="H13" s="12" t="s">
+      <c r="H13" s="11" t="s">
         <v>236</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A14" s="13">
+      <c r="A14" s="12">
         <v>10</v>
       </c>
-      <c r="B14" s="12" t="s">
+      <c r="B14" s="11" t="s">
         <v>237</v>
       </c>
-      <c r="C14" s="13" t="s">
+      <c r="C14" s="12" t="s">
         <v>225</v>
       </c>
-      <c r="D14" s="14">
+      <c r="D14" s="13">
         <v>1</v>
       </c>
-      <c r="E14" s="14">
+      <c r="E14" s="13">
         <v>2</v>
       </c>
-      <c r="F14" s="32" t="str">
+      <c r="F14" s="27" t="str">
         <f t="shared" si="0"/>
         <v>C</v>
       </c>
-      <c r="G14" s="12" t="str">
+      <c r="G14" s="11" t="str">
         <f t="shared" si="1"/>
         <v>Минимальный контроль</v>
       </c>
-      <c r="H14" s="12" t="s">
+      <c r="H14" s="11" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A15" s="13">
+    <row r="15" spans="1:8" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A15" s="12">
         <v>11</v>
       </c>
-      <c r="B15" s="12" t="s">
+      <c r="B15" s="11" t="s">
         <v>239</v>
       </c>
-      <c r="C15" s="13" t="s">
+      <c r="C15" s="12" t="s">
         <v>225</v>
       </c>
-      <c r="D15" s="14">
+      <c r="D15" s="13">
         <v>2</v>
       </c>
-      <c r="E15" s="14">
+      <c r="E15" s="13">
         <v>1</v>
       </c>
-      <c r="F15" s="32" t="str">
+      <c r="F15" s="27" t="str">
         <f t="shared" si="0"/>
         <v>C</v>
       </c>
-      <c r="G15" s="12" t="str">
+      <c r="G15" s="11" t="str">
         <f t="shared" si="1"/>
         <v>Минимальный контроль</v>
       </c>
-      <c r="H15" s="12" t="s">
+      <c r="H15" s="11" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="42.75" x14ac:dyDescent="0.45">
-      <c r="A16" s="13">
+    <row r="16" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A16" s="12">
         <v>12</v>
       </c>
-      <c r="B16" s="12" t="s">
+      <c r="B16" s="11" t="s">
         <v>241</v>
       </c>
-      <c r="C16" s="13" t="s">
+      <c r="C16" s="12" t="s">
         <v>225</v>
       </c>
-      <c r="D16" s="14">
+      <c r="D16" s="13">
         <v>2</v>
       </c>
-      <c r="E16" s="14">
+      <c r="E16" s="13">
         <v>3</v>
       </c>
-      <c r="F16" s="32" t="str">
+      <c r="F16" s="27" t="str">
         <f t="shared" si="0"/>
         <v>C</v>
       </c>
-      <c r="G16" s="12" t="str">
+      <c r="G16" s="11" t="str">
         <f t="shared" si="1"/>
         <v>Минимальный контроль</v>
       </c>
-      <c r="H16" s="12" t="s">
+      <c r="H16" s="11" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A17" s="13">
+    <row r="17" spans="1:8" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A17" s="12">
         <v>13</v>
       </c>
-      <c r="B17" s="12" t="s">
+      <c r="B17" s="11" t="s">
         <v>243</v>
       </c>
-      <c r="C17" s="13" t="s">
+      <c r="C17" s="12" t="s">
         <v>225</v>
       </c>
-      <c r="D17" s="14">
+      <c r="D17" s="13">
         <v>1</v>
       </c>
-      <c r="E17" s="14">
+      <c r="E17" s="13">
         <v>2</v>
       </c>
-      <c r="F17" s="32" t="str">
+      <c r="F17" s="27" t="str">
         <f t="shared" si="0"/>
         <v>C</v>
       </c>
-      <c r="G17" s="12" t="str">
+      <c r="G17" s="11" t="str">
         <f t="shared" si="1"/>
         <v>Минимальный контроль</v>
       </c>
-      <c r="H17" s="12" t="s">
+      <c r="H17" s="11" t="s">
         <v>244</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A18" s="9"/>
-      <c r="B18" s="9"/>
-      <c r="C18" s="9"/>
-      <c r="D18" s="9"/>
-      <c r="E18" s="9"/>
-      <c r="F18" s="9"/>
-      <c r="G18" s="9"/>
-      <c r="H18" s="9"/>
+      <c r="A18" s="8"/>
+      <c r="B18" s="8"/>
+      <c r="C18" s="8"/>
+      <c r="D18" s="8"/>
+      <c r="E18" s="8"/>
+      <c r="F18" s="8"/>
+      <c r="G18" s="8"/>
+      <c r="H18" s="8"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A19" s="9"/>
-      <c r="B19" s="9"/>
-      <c r="C19" s="9"/>
-      <c r="D19" s="9"/>
-      <c r="E19" s="9"/>
-      <c r="F19" s="9"/>
-      <c r="G19" s="9"/>
-      <c r="H19" s="9"/>
-    </row>
-    <row r="20" spans="1:8" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="A19" s="8"/>
+      <c r="B19" s="8"/>
+      <c r="C19" s="8"/>
+      <c r="D19" s="8"/>
+      <c r="E19" s="8"/>
+      <c r="F19" s="8"/>
+      <c r="G19" s="8"/>
+      <c r="H19" s="8"/>
+    </row>
+    <row r="20" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A20" s="1" t="s">
         <v>215</v>
       </c>
@@ -4103,101 +4103,101 @@
       <c r="D20" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="E20" s="9"/>
-      <c r="F20" s="9"/>
-      <c r="G20" s="9"/>
-      <c r="H20" s="9"/>
+      <c r="E20" s="8"/>
+      <c r="F20" s="8"/>
+      <c r="G20" s="8"/>
+      <c r="H20" s="8"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A21" s="32" t="s">
+      <c r="A21" s="27" t="s">
         <v>246</v>
       </c>
-      <c r="B21" s="12" t="s">
+      <c r="B21" s="11" t="s">
         <v>247</v>
       </c>
-      <c r="C21" s="12" t="s">
+      <c r="C21" s="11" t="s">
         <v>248</v>
       </c>
-      <c r="D21" s="13">
+      <c r="D21" s="12">
         <f>COUNTIF($F$5:$F$17,A21)</f>
         <v>2</v>
       </c>
-      <c r="E21" s="9"/>
-      <c r="F21" s="9"/>
-      <c r="G21" s="9"/>
-      <c r="H21" s="9"/>
+      <c r="E21" s="8"/>
+      <c r="F21" s="8"/>
+      <c r="G21" s="8"/>
+      <c r="H21" s="8"/>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A22" s="32" t="s">
+      <c r="A22" s="27" t="s">
         <v>249</v>
       </c>
-      <c r="B22" s="12" t="s">
+      <c r="B22" s="11" t="s">
         <v>250</v>
       </c>
-      <c r="C22" s="12" t="s">
+      <c r="C22" s="11" t="s">
         <v>251</v>
       </c>
-      <c r="D22" s="13">
+      <c r="D22" s="12">
         <f>COUNTIF($F$5:$F$17,A22)</f>
         <v>3</v>
       </c>
-      <c r="E22" s="9"/>
-      <c r="F22" s="9"/>
-      <c r="G22" s="9"/>
-      <c r="H22" s="9"/>
+      <c r="E22" s="8"/>
+      <c r="F22" s="8"/>
+      <c r="G22" s="8"/>
+      <c r="H22" s="8"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A23" s="32" t="s">
+      <c r="A23" s="27" t="s">
         <v>252</v>
       </c>
-      <c r="B23" s="12" t="s">
+      <c r="B23" s="11" t="s">
         <v>253</v>
       </c>
-      <c r="C23" s="12" t="s">
+      <c r="C23" s="11" t="s">
         <v>254</v>
       </c>
-      <c r="D23" s="13">
+      <c r="D23" s="12">
         <f>COUNTIF($F$5:$F$17,A23)</f>
         <v>5</v>
       </c>
-      <c r="E23" s="9"/>
-      <c r="F23" s="9"/>
-      <c r="G23" s="9"/>
-      <c r="H23" s="9"/>
+      <c r="E23" s="8"/>
+      <c r="F23" s="8"/>
+      <c r="G23" s="8"/>
+      <c r="H23" s="8"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A24" s="32" t="s">
+      <c r="A24" s="27" t="s">
         <v>255</v>
       </c>
-      <c r="B24" s="12" t="s">
+      <c r="B24" s="11" t="s">
         <v>256</v>
       </c>
-      <c r="C24" s="12" t="s">
+      <c r="C24" s="11" t="s">
         <v>257</v>
       </c>
-      <c r="D24" s="13">
+      <c r="D24" s="12">
         <f>COUNTIF($F$5:$F$17,A24)</f>
         <v>3</v>
       </c>
-      <c r="E24" s="9"/>
-      <c r="F24" s="9"/>
-      <c r="G24" s="9"/>
-      <c r="H24" s="9"/>
+      <c r="E24" s="8"/>
+      <c r="F24" s="8"/>
+      <c r="G24" s="8"/>
+      <c r="H24" s="8"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A25" s="17"/>
-      <c r="B25" s="17" t="s">
+      <c r="A25" s="16"/>
+      <c r="B25" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="C25" s="17"/>
-      <c r="D25" s="29">
+      <c r="C25" s="16"/>
+      <c r="D25" s="24">
         <f>SUM(D21:D24)</f>
         <v>13</v>
       </c>
-      <c r="E25" s="9"/>
-      <c r="F25" s="9"/>
-      <c r="G25" s="9"/>
-      <c r="H25" s="9"/>
+      <c r="E25" s="8"/>
+      <c r="F25" s="8"/>
+      <c r="G25" s="8"/>
+      <c r="H25" s="8"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="F5:G17">
@@ -4215,10 +4215,10 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" scale="62" fitToHeight="0" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="62" fitToHeight="0" orientation="landscape"/>
   <headerFooter>
     <oddFooter>&amp;C&amp;P / &amp;N</oddFooter>
   </headerFooter>
-  <drawing r:id="rId2"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>